--- a/data/databook.xlsx
+++ b/data/databook.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="684">
   <si>
     <t>profile_id</t>
   </si>
@@ -158,10 +158,7 @@
     <t>PAGE-001</t>
   </si>
   <si>
-    <t>Test 1</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/profile.php?id=61595080421933</t>
+    <t>PAUSED</t>
   </si>
   <si>
     <t>PAGE-002</t>
@@ -319,17 +316,36 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <color rgb="FF800080"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">FULL STORY IN HERE ❤👇👇:
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF800080"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF800080"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">👇👇:
 </t>
     </r>
     <r>
       <rPr>
         <u/>
         <sz val="10"/>
-        <color rgb="FF1155CC"/>
+        <color rgb="FF800080"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -14971,7 +14987,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -14993,6 +15009,12 @@
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -15167,6 +15189,19 @@
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -15542,31 +15577,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -15575,115 +15607,118 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -15707,20 +15742,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="6" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="6" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16523,31 +16558,25 @@
       <c r="A2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
       <c r="A3" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>45</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>46</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>7</v>
@@ -16555,7 +16584,7 @@
     </row>
     <row r="4" customHeight="1" spans="1:5">
       <c r="A4" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -16564,7 +16593,7 @@
     </row>
     <row r="5" customHeight="1" spans="1:5">
       <c r="A5" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -16573,7 +16602,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:5">
       <c r="A6" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -16582,7 +16611,7 @@
     </row>
     <row r="7" customHeight="1" spans="1:5">
       <c r="A7" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -16591,7 +16620,7 @@
     </row>
     <row r="8" customHeight="1" spans="1:5">
       <c r="A8" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -16600,7 +16629,7 @@
     </row>
     <row r="9" customHeight="1" spans="1:5">
       <c r="A9" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -16609,7 +16638,7 @@
     </row>
     <row r="10" customHeight="1" spans="1:5">
       <c r="A10" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -16618,7 +16647,7 @@
     </row>
     <row r="11" customHeight="1" spans="1:5">
       <c r="A11" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -16627,7 +16656,7 @@
     </row>
     <row r="12" customHeight="1" spans="1:5">
       <c r="A12" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -16636,7 +16665,7 @@
     </row>
     <row r="13" customHeight="1" spans="1:5">
       <c r="A13" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -16645,7 +16674,7 @@
     </row>
     <row r="14" customHeight="1" spans="1:5">
       <c r="A14" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -16654,7 +16683,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:5">
       <c r="A15" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -16663,7 +16692,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:5">
       <c r="A16" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -16672,7 +16701,7 @@
     </row>
     <row r="17" customHeight="1" spans="1:5">
       <c r="A17" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -16681,7 +16710,7 @@
     </row>
     <row r="18" customHeight="1" spans="1:5">
       <c r="A18" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -16690,7 +16719,7 @@
     </row>
     <row r="19" customHeight="1" spans="1:5">
       <c r="A19" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -16699,7 +16728,7 @@
     </row>
     <row r="20" customHeight="1" spans="1:5">
       <c r="A20" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -16708,7 +16737,7 @@
     </row>
     <row r="21" customHeight="1" spans="1:5">
       <c r="A21" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -16722,8 +16751,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://www.facebook.com/profile.php?id=61595080421933"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://www.facebook.com/profile.php?id=61594947346869"/>
+    <hyperlink ref="D3" r:id="rId1" display="https://www.facebook.com/profile.php?id=61594947346869"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -16745,42 +16773,38 @@
   <sheetData>
     <row r="1" ht="12.75" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:26">
       <c r="A2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -16805,22 +16829,22 @@
     </row>
     <row r="3" customHeight="1" spans="1:26">
       <c r="A3" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="5">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -16845,22 +16869,18 @@
     </row>
     <row r="4" customHeight="1" spans="1:26">
       <c r="A4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="5">
-        <v>2</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -16885,22 +16905,22 @@
     </row>
     <row r="5" customHeight="1" spans="1:26">
       <c r="A5" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="5">
         <v>2</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -16925,22 +16945,18 @@
     </row>
     <row r="6" customHeight="1" spans="1:26">
       <c r="A6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="6">
-        <v>3</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -16965,22 +16981,22 @@
     </row>
     <row r="7" customHeight="1" spans="1:26">
       <c r="A7" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -17005,22 +17021,18 @@
     </row>
     <row r="8" customHeight="1" spans="1:26">
       <c r="A8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="5">
-        <v>4</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -17045,22 +17057,22 @@
     </row>
     <row r="9" customHeight="1" spans="1:26">
       <c r="A9" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="5">
         <v>4</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -17085,22 +17097,18 @@
     </row>
     <row r="10" customHeight="1" spans="1:26">
       <c r="A10" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="5">
-        <v>5</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -17125,22 +17133,22 @@
     </row>
     <row r="11" customHeight="1" spans="1:26">
       <c r="A11" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" s="6">
         <v>5</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -17165,18 +17173,18 @@
     </row>
     <row r="12" customHeight="1" spans="1:26">
       <c r="A12" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -17201,18 +17209,18 @@
     </row>
     <row r="13" customHeight="1" spans="1:26">
       <c r="A13" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -17237,18 +17245,18 @@
     </row>
     <row r="14" customHeight="1" spans="1:26">
       <c r="A14" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -17273,18 +17281,18 @@
     </row>
     <row r="15" customHeight="1" spans="1:26">
       <c r="A15" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -17309,18 +17317,18 @@
     </row>
     <row r="16" customHeight="1" spans="1:26">
       <c r="A16" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -17345,16 +17353,16 @@
     </row>
     <row r="17" customHeight="1" spans="1:26">
       <c r="A17" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -17379,16 +17387,16 @@
     </row>
     <row r="18" customHeight="1" spans="1:26">
       <c r="A18" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -17413,16 +17421,16 @@
     </row>
     <row r="19" customHeight="1" spans="1:26">
       <c r="A19" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -17447,16 +17455,16 @@
     </row>
     <row r="20" customHeight="1" spans="1:26">
       <c r="A20" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -17481,16 +17489,16 @@
     </row>
     <row r="21" customHeight="1" spans="1:26">
       <c r="A21" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -17515,16 +17523,16 @@
     </row>
     <row r="22" customHeight="1" spans="1:26">
       <c r="A22" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -17549,16 +17557,16 @@
     </row>
     <row r="23" customHeight="1" spans="1:26">
       <c r="A23" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -17583,16 +17591,16 @@
     </row>
     <row r="24" customHeight="1" spans="1:26">
       <c r="A24" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -17617,16 +17625,16 @@
     </row>
     <row r="25" customHeight="1" spans="1:26">
       <c r="A25" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -17651,16 +17659,16 @@
     </row>
     <row r="26" customHeight="1" spans="1:26">
       <c r="A26" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -17685,16 +17693,16 @@
     </row>
     <row r="27" customHeight="1" spans="1:26">
       <c r="A27" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -17719,16 +17727,16 @@
     </row>
     <row r="28" customHeight="1" spans="1:26">
       <c r="A28" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -17753,16 +17761,16 @@
     </row>
     <row r="29" customHeight="1" spans="1:26">
       <c r="A29" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -17787,16 +17795,16 @@
     </row>
     <row r="30" customHeight="1" spans="1:26">
       <c r="A30" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -17821,16 +17829,16 @@
     </row>
     <row r="31" customHeight="1" spans="1:26">
       <c r="A31" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -17855,16 +17863,16 @@
     </row>
     <row r="32" customHeight="1" spans="1:26">
       <c r="A32" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -17889,16 +17897,16 @@
     </row>
     <row r="33" customHeight="1" spans="1:26">
       <c r="A33" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -17923,16 +17931,16 @@
     </row>
     <row r="34" customHeight="1" spans="1:26">
       <c r="A34" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -17957,16 +17965,16 @@
     </row>
     <row r="35" customHeight="1" spans="1:26">
       <c r="A35" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -17991,16 +17999,16 @@
     </row>
     <row r="36" customHeight="1" spans="1:26">
       <c r="A36" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -18025,16 +18033,16 @@
     </row>
     <row r="37" customHeight="1" spans="1:26">
       <c r="A37" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -18059,16 +18067,16 @@
     </row>
     <row r="38" customHeight="1" spans="1:26">
       <c r="A38" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -18093,16 +18101,16 @@
     </row>
     <row r="39" customHeight="1" spans="1:26">
       <c r="A39" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -18127,16 +18135,16 @@
     </row>
     <row r="40" customHeight="1" spans="1:26">
       <c r="A40" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -18161,16 +18169,16 @@
     </row>
     <row r="41" customHeight="1" spans="1:26">
       <c r="A41" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -18195,16 +18203,16 @@
     </row>
     <row r="42" customHeight="1" spans="1:26">
       <c r="A42" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -18229,16 +18237,16 @@
     </row>
     <row r="43" customHeight="1" spans="1:26">
       <c r="A43" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -18263,16 +18271,16 @@
     </row>
     <row r="44" customHeight="1" spans="1:26">
       <c r="A44" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -18297,16 +18305,16 @@
     </row>
     <row r="45" customHeight="1" spans="1:26">
       <c r="A45" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -18331,16 +18339,16 @@
     </row>
     <row r="46" customHeight="1" spans="1:26">
       <c r="A46" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -18365,16 +18373,16 @@
     </row>
     <row r="47" customHeight="1" spans="1:26">
       <c r="A47" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -18399,16 +18407,16 @@
     </row>
     <row r="48" customHeight="1" spans="1:26">
       <c r="A48" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -18433,16 +18441,16 @@
     </row>
     <row r="49" customHeight="1" spans="1:26">
       <c r="A49" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -18467,16 +18475,16 @@
     </row>
     <row r="50" customHeight="1" spans="1:26">
       <c r="A50" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -18501,16 +18509,16 @@
     </row>
     <row r="51" customHeight="1" spans="1:26">
       <c r="A51" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -18535,16 +18543,16 @@
     </row>
     <row r="52" customHeight="1" spans="1:26">
       <c r="A52" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -18569,16 +18577,16 @@
     </row>
     <row r="53" customHeight="1" spans="1:26">
       <c r="A53" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -18603,16 +18611,16 @@
     </row>
     <row r="54" customHeight="1" spans="1:26">
       <c r="A54" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -18637,16 +18645,16 @@
     </row>
     <row r="55" customHeight="1" spans="1:26">
       <c r="A55" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -18671,16 +18679,16 @@
     </row>
     <row r="56" customHeight="1" spans="1:26">
       <c r="A56" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E56" s="6"/>
       <c r="F56" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -18705,16 +18713,16 @@
     </row>
     <row r="57" customHeight="1" spans="1:26">
       <c r="A57" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -18739,16 +18747,16 @@
     </row>
     <row r="58" customHeight="1" spans="1:26">
       <c r="A58" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -18773,16 +18781,16 @@
     </row>
     <row r="59" customHeight="1" spans="1:26">
       <c r="A59" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -18807,16 +18815,16 @@
     </row>
     <row r="60" customHeight="1" spans="1:26">
       <c r="A60" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -18841,16 +18849,16 @@
     </row>
     <row r="61" customHeight="1" spans="1:26">
       <c r="A61" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -18875,16 +18883,16 @@
     </row>
     <row r="62" customHeight="1" spans="1:26">
       <c r="A62" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
@@ -18909,16 +18917,16 @@
     </row>
     <row r="63" customHeight="1" spans="1:26">
       <c r="A63" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -18943,16 +18951,16 @@
     </row>
     <row r="64" customHeight="1" spans="1:26">
       <c r="A64" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -18977,16 +18985,16 @@
     </row>
     <row r="65" customHeight="1" spans="1:26">
       <c r="A65" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
@@ -19011,16 +19019,16 @@
     </row>
     <row r="66" customHeight="1" spans="1:26">
       <c r="A66" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -19045,16 +19053,16 @@
     </row>
     <row r="67" customHeight="1" spans="1:26">
       <c r="A67" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -19079,16 +19087,16 @@
     </row>
     <row r="68" customHeight="1" spans="1:26">
       <c r="A68" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
       <c r="D68" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
@@ -19113,16 +19121,16 @@
     </row>
     <row r="69" customHeight="1" spans="1:26">
       <c r="A69" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
       <c r="D69" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
@@ -19147,16 +19155,16 @@
     </row>
     <row r="70" customHeight="1" spans="1:26">
       <c r="A70" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
       <c r="D70" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -19181,16 +19189,16 @@
     </row>
     <row r="71" customHeight="1" spans="1:26">
       <c r="A71" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
@@ -19215,16 +19223,16 @@
     </row>
     <row r="72" customHeight="1" spans="1:26">
       <c r="A72" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
@@ -19249,16 +19257,16 @@
     </row>
     <row r="73" customHeight="1" spans="1:26">
       <c r="A73" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
@@ -19283,16 +19291,16 @@
     </row>
     <row r="74" customHeight="1" spans="1:26">
       <c r="A74" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
@@ -19317,16 +19325,16 @@
     </row>
     <row r="75" customHeight="1" spans="1:26">
       <c r="A75" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
@@ -19351,16 +19359,16 @@
     </row>
     <row r="76" customHeight="1" spans="1:26">
       <c r="A76" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
       <c r="D76" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -19385,16 +19393,16 @@
     </row>
     <row r="77" customHeight="1" spans="1:26">
       <c r="A77" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
@@ -19419,16 +19427,16 @@
     </row>
     <row r="78" customHeight="1" spans="1:26">
       <c r="A78" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
@@ -19453,16 +19461,16 @@
     </row>
     <row r="79" customHeight="1" spans="1:26">
       <c r="A79" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
@@ -19487,16 +19495,16 @@
     </row>
     <row r="80" customHeight="1" spans="1:26">
       <c r="A80" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
@@ -19521,16 +19529,16 @@
     </row>
     <row r="81" customHeight="1" spans="1:26">
       <c r="A81" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
       <c r="D81" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
@@ -19555,16 +19563,16 @@
     </row>
     <row r="82" customHeight="1" spans="1:26">
       <c r="A82" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
@@ -19589,16 +19597,16 @@
     </row>
     <row r="83" customHeight="1" spans="1:26">
       <c r="A83" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E83" s="5"/>
       <c r="F83" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
@@ -19623,16 +19631,16 @@
     </row>
     <row r="84" customHeight="1" spans="1:26">
       <c r="A84" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E84" s="5"/>
       <c r="F84" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
@@ -19657,16 +19665,16 @@
     </row>
     <row r="85" customHeight="1" spans="1:26">
       <c r="A85" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
       <c r="D85" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E85" s="5"/>
       <c r="F85" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
@@ -19691,16 +19699,16 @@
     </row>
     <row r="86" customHeight="1" spans="1:26">
       <c r="A86" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E86" s="6"/>
       <c r="F86" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
@@ -19725,16 +19733,16 @@
     </row>
     <row r="87" customHeight="1" spans="1:26">
       <c r="A87" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
@@ -19759,16 +19767,16 @@
     </row>
     <row r="88" customHeight="1" spans="1:26">
       <c r="A88" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
       <c r="D88" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E88" s="5"/>
       <c r="F88" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
@@ -19793,16 +19801,16 @@
     </row>
     <row r="89" customHeight="1" spans="1:26">
       <c r="A89" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
       <c r="D89" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E89" s="5"/>
       <c r="F89" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
@@ -19827,16 +19835,16 @@
     </row>
     <row r="90" customHeight="1" spans="1:26">
       <c r="A90" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
       <c r="D90" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E90" s="5"/>
       <c r="F90" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
@@ -19861,16 +19869,16 @@
     </row>
     <row r="91" customHeight="1" spans="1:26">
       <c r="A91" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E91" s="6"/>
       <c r="F91" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
@@ -19895,16 +19903,16 @@
     </row>
     <row r="92" customHeight="1" spans="1:26">
       <c r="A92" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
@@ -19929,16 +19937,16 @@
     </row>
     <row r="93" customHeight="1" spans="1:26">
       <c r="A93" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
@@ -19963,16 +19971,16 @@
     </row>
     <row r="94" customHeight="1" spans="1:26">
       <c r="A94" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
       <c r="D94" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E94" s="5"/>
       <c r="F94" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
@@ -19997,16 +20005,16 @@
     </row>
     <row r="95" customHeight="1" spans="1:26">
       <c r="A95" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E95" s="5"/>
       <c r="F95" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
@@ -20031,16 +20039,16 @@
     </row>
     <row r="96" customHeight="1" spans="1:26">
       <c r="A96" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
       <c r="D96" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
@@ -20065,16 +20073,16 @@
     </row>
     <row r="97" customHeight="1" spans="1:26">
       <c r="A97" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
@@ -20099,16 +20107,16 @@
     </row>
     <row r="98" customHeight="1" spans="1:26">
       <c r="A98" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E98" s="5"/>
       <c r="F98" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
@@ -20133,16 +20141,16 @@
     </row>
     <row r="99" customHeight="1" spans="1:26">
       <c r="A99" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E99" s="5"/>
       <c r="F99" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
@@ -20167,16 +20175,16 @@
     </row>
     <row r="100" customHeight="1" spans="1:26">
       <c r="A100" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
       <c r="D100" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E100" s="5"/>
       <c r="F100" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
@@ -20201,16 +20209,16 @@
     </row>
     <row r="101" customHeight="1" spans="1:26">
       <c r="A101" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
       <c r="D101" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
@@ -20235,16 +20243,16 @@
     </row>
     <row r="102" customHeight="1" spans="1:26">
       <c r="A102" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
@@ -20269,16 +20277,16 @@
     </row>
     <row r="103" customHeight="1" spans="1:26">
       <c r="A103" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
       <c r="D103" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
@@ -20303,16 +20311,16 @@
     </row>
     <row r="104" customHeight="1" spans="1:26">
       <c r="A104" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
       <c r="D104" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
@@ -20337,16 +20345,16 @@
     </row>
     <row r="105" customHeight="1" spans="1:26">
       <c r="A105" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
       <c r="D105" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
@@ -20371,16 +20379,16 @@
     </row>
     <row r="106" customHeight="1" spans="1:26">
       <c r="A106" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
@@ -20405,16 +20413,16 @@
     </row>
     <row r="107" customHeight="1" spans="1:26">
       <c r="A107" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
@@ -20439,16 +20447,16 @@
     </row>
     <row r="108" customHeight="1" spans="1:26">
       <c r="A108" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
       <c r="D108" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
@@ -20473,16 +20481,16 @@
     </row>
     <row r="109" customHeight="1" spans="1:26">
       <c r="A109" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
       <c r="D109" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E109" s="5"/>
       <c r="F109" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
@@ -20507,16 +20515,16 @@
     </row>
     <row r="110" customHeight="1" spans="1:26">
       <c r="A110" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
       <c r="D110" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E110" s="5"/>
       <c r="F110" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
@@ -20541,16 +20549,16 @@
     </row>
     <row r="111" customHeight="1" spans="1:26">
       <c r="A111" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
       <c r="D111" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
@@ -20575,16 +20583,16 @@
     </row>
     <row r="112" customHeight="1" spans="1:26">
       <c r="A112" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
@@ -20609,16 +20617,16 @@
     </row>
     <row r="113" customHeight="1" spans="1:26">
       <c r="A113" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
       <c r="D113" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E113" s="5"/>
       <c r="F113" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
@@ -20643,16 +20651,16 @@
     </row>
     <row r="114" customHeight="1" spans="1:26">
       <c r="A114" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
       <c r="D114" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E114" s="5"/>
       <c r="F114" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
@@ -20677,16 +20685,16 @@
     </row>
     <row r="115" customHeight="1" spans="1:26">
       <c r="A115" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
       <c r="D115" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E115" s="5"/>
       <c r="F115" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
@@ -20711,16 +20719,16 @@
     </row>
     <row r="116" customHeight="1" spans="1:26">
       <c r="A116" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
       <c r="D116" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E116" s="6"/>
       <c r="F116" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
@@ -20745,16 +20753,16 @@
     </row>
     <row r="117" customHeight="1" spans="1:26">
       <c r="A117" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
@@ -20779,16 +20787,16 @@
     </row>
     <row r="118" customHeight="1" spans="1:26">
       <c r="A118" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
       <c r="D118" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
@@ -20813,16 +20821,16 @@
     </row>
     <row r="119" customHeight="1" spans="1:26">
       <c r="A119" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
       <c r="D119" s="5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
@@ -20847,16 +20855,16 @@
     </row>
     <row r="120" customHeight="1" spans="1:26">
       <c r="A120" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
       <c r="D120" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
@@ -20881,16 +20889,16 @@
     </row>
     <row r="121" customHeight="1" spans="1:26">
       <c r="A121" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
       <c r="D121" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E121" s="6"/>
       <c r="F121" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
@@ -20915,16 +20923,16 @@
     </row>
     <row r="122" customHeight="1" spans="1:26">
       <c r="A122" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
@@ -20949,16 +20957,16 @@
     </row>
     <row r="123" customHeight="1" spans="1:26">
       <c r="A123" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
       <c r="D123" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
@@ -20983,16 +20991,16 @@
     </row>
     <row r="124" customHeight="1" spans="1:26">
       <c r="A124" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
       <c r="D124" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
@@ -21017,16 +21025,16 @@
     </row>
     <row r="125" customHeight="1" spans="1:26">
       <c r="A125" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
       <c r="D125" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E125" s="5"/>
       <c r="F125" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
@@ -21051,16 +21059,16 @@
     </row>
     <row r="126" customHeight="1" spans="1:26">
       <c r="A126" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
       <c r="D126" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
@@ -21085,16 +21093,16 @@
     </row>
     <row r="127" customHeight="1" spans="1:26">
       <c r="A127" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
@@ -21119,16 +21127,16 @@
     </row>
     <row r="128" customHeight="1" spans="1:26">
       <c r="A128" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
       <c r="D128" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
@@ -21153,16 +21161,16 @@
     </row>
     <row r="129" customHeight="1" spans="1:26">
       <c r="A129" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
       <c r="D129" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
@@ -21187,16 +21195,16 @@
     </row>
     <row r="130" customHeight="1" spans="1:26">
       <c r="A130" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
       <c r="D130" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
@@ -21221,16 +21229,16 @@
     </row>
     <row r="131" customHeight="1" spans="1:26">
       <c r="A131" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
       <c r="D131" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
@@ -21255,16 +21263,16 @@
     </row>
     <row r="132" customHeight="1" spans="1:26">
       <c r="A132" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
@@ -21289,16 +21297,16 @@
     </row>
     <row r="133" customHeight="1" spans="1:26">
       <c r="A133" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
       <c r="D133" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
@@ -21323,16 +21331,16 @@
     </row>
     <row r="134" customHeight="1" spans="1:26">
       <c r="A134" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
       <c r="D134" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
@@ -21357,16 +21365,16 @@
     </row>
     <row r="135" customHeight="1" spans="1:26">
       <c r="A135" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
       <c r="D135" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
@@ -21391,16 +21399,16 @@
     </row>
     <row r="136" customHeight="1" spans="1:26">
       <c r="A136" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
       <c r="D136" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E136" s="6"/>
       <c r="F136" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
@@ -21425,16 +21433,16 @@
     </row>
     <row r="137" customHeight="1" spans="1:26">
       <c r="A137" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
@@ -21459,16 +21467,16 @@
     </row>
     <row r="138" customHeight="1" spans="1:26">
       <c r="A138" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
       <c r="D138" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E138" s="5"/>
       <c r="F138" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
@@ -21493,16 +21501,16 @@
     </row>
     <row r="139" customHeight="1" spans="1:26">
       <c r="A139" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
       <c r="D139" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E139" s="5"/>
       <c r="F139" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
@@ -21527,16 +21535,16 @@
     </row>
     <row r="140" customHeight="1" spans="1:26">
       <c r="A140" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
       <c r="D140" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E140" s="5"/>
       <c r="F140" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
@@ -21561,16 +21569,16 @@
     </row>
     <row r="141" customHeight="1" spans="1:26">
       <c r="A141" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
       <c r="D141" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
@@ -21595,16 +21603,16 @@
     </row>
     <row r="142" customHeight="1" spans="1:26">
       <c r="A142" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
@@ -21629,16 +21637,16 @@
     </row>
     <row r="143" customHeight="1" spans="1:26">
       <c r="A143" s="5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
       <c r="D143" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
@@ -21663,16 +21671,16 @@
     </row>
     <row r="144" customHeight="1" spans="1:26">
       <c r="A144" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
       <c r="D144" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E144" s="5"/>
       <c r="F144" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
@@ -21697,16 +21705,16 @@
     </row>
     <row r="145" customHeight="1" spans="1:26">
       <c r="A145" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
       <c r="D145" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
@@ -21731,16 +21739,16 @@
     </row>
     <row r="146" customHeight="1" spans="1:26">
       <c r="A146" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
       <c r="D146" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E146" s="6"/>
       <c r="F146" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
@@ -21765,16 +21773,16 @@
     </row>
     <row r="147" customHeight="1" spans="1:26">
       <c r="A147" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
@@ -21799,16 +21807,16 @@
     </row>
     <row r="148" customHeight="1" spans="1:26">
       <c r="A148" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
       <c r="D148" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E148" s="5"/>
       <c r="F148" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
@@ -21833,16 +21841,16 @@
     </row>
     <row r="149" customHeight="1" spans="1:26">
       <c r="A149" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
       <c r="D149" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E149" s="5"/>
       <c r="F149" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
@@ -21867,16 +21875,16 @@
     </row>
     <row r="150" customHeight="1" spans="1:26">
       <c r="A150" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
       <c r="D150" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E150" s="5"/>
       <c r="F150" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
@@ -21901,16 +21909,16 @@
     </row>
     <row r="151" customHeight="1" spans="1:26">
       <c r="A151" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
       <c r="D151" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E151" s="6"/>
       <c r="F151" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
@@ -21935,16 +21943,16 @@
     </row>
     <row r="152" customHeight="1" spans="1:26">
       <c r="A152" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
@@ -21969,16 +21977,16 @@
     </row>
     <row r="153" customHeight="1" spans="1:26">
       <c r="A153" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
       <c r="D153" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E153" s="5"/>
       <c r="F153" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
@@ -22003,16 +22011,16 @@
     </row>
     <row r="154" customHeight="1" spans="1:26">
       <c r="A154" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
       <c r="D154" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E154" s="5"/>
       <c r="F154" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
@@ -22037,16 +22045,16 @@
     </row>
     <row r="155" customHeight="1" spans="1:26">
       <c r="A155" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
       <c r="D155" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
@@ -22071,16 +22079,16 @@
     </row>
     <row r="156" customHeight="1" spans="1:26">
       <c r="A156" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
       <c r="D156" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G156" s="4"/>
       <c r="H156" s="4"/>
@@ -22105,16 +22113,16 @@
     </row>
     <row r="157" customHeight="1" spans="1:26">
       <c r="A157" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
@@ -22139,16 +22147,16 @@
     </row>
     <row r="158" customHeight="1" spans="1:26">
       <c r="A158" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
       <c r="D158" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E158" s="5"/>
       <c r="F158" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G158" s="4"/>
       <c r="H158" s="4"/>
@@ -22173,16 +22181,16 @@
     </row>
     <row r="159" customHeight="1" spans="1:26">
       <c r="A159" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
       <c r="D159" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E159" s="5"/>
       <c r="F159" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
@@ -22207,16 +22215,16 @@
     </row>
     <row r="160" customHeight="1" spans="1:26">
       <c r="A160" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
       <c r="D160" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E160" s="5"/>
       <c r="F160" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G160" s="4"/>
       <c r="H160" s="4"/>
@@ -22241,16 +22249,16 @@
     </row>
     <row r="161" customHeight="1" spans="1:26">
       <c r="A161" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
       <c r="D161" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
@@ -22275,16 +22283,16 @@
     </row>
     <row r="162" customHeight="1" spans="1:26">
       <c r="A162" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
@@ -22309,16 +22317,16 @@
     </row>
     <row r="163" customHeight="1" spans="1:26">
       <c r="A163" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
       <c r="D163" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E163" s="5"/>
       <c r="F163" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G163" s="4"/>
       <c r="H163" s="4"/>
@@ -22343,16 +22351,16 @@
     </row>
     <row r="164" customHeight="1" spans="1:26">
       <c r="A164" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
       <c r="D164" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E164" s="5"/>
       <c r="F164" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G164" s="4"/>
       <c r="H164" s="4"/>
@@ -22377,16 +22385,16 @@
     </row>
     <row r="165" customHeight="1" spans="1:26">
       <c r="A165" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
       <c r="D165" s="5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E165" s="5"/>
       <c r="F165" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G165" s="4"/>
       <c r="H165" s="4"/>
@@ -22411,16 +22419,16 @@
     </row>
     <row r="166" customHeight="1" spans="1:26">
       <c r="A166" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
       <c r="D166" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E166" s="6"/>
       <c r="F166" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G166" s="4"/>
       <c r="H166" s="4"/>
@@ -22445,16 +22453,16 @@
     </row>
     <row r="167" customHeight="1" spans="1:26">
       <c r="A167" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G167" s="4"/>
       <c r="H167" s="4"/>
@@ -22479,16 +22487,16 @@
     </row>
     <row r="168" customHeight="1" spans="1:26">
       <c r="A168" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
       <c r="D168" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E168" s="5"/>
       <c r="F168" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G168" s="4"/>
       <c r="H168" s="4"/>
@@ -22513,16 +22521,16 @@
     </row>
     <row r="169" customHeight="1" spans="1:26">
       <c r="A169" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
       <c r="D169" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E169" s="5"/>
       <c r="F169" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G169" s="4"/>
       <c r="H169" s="4"/>
@@ -22547,16 +22555,16 @@
     </row>
     <row r="170" customHeight="1" spans="1:26">
       <c r="A170" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
       <c r="D170" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E170" s="5"/>
       <c r="F170" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G170" s="4"/>
       <c r="H170" s="4"/>
@@ -22581,16 +22589,16 @@
     </row>
     <row r="171" customHeight="1" spans="1:26">
       <c r="A171" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
       <c r="D171" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E171" s="6"/>
       <c r="F171" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G171" s="4"/>
       <c r="H171" s="4"/>
@@ -22615,16 +22623,16 @@
     </row>
     <row r="172" customHeight="1" spans="1:26">
       <c r="A172" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
@@ -22649,16 +22657,16 @@
     </row>
     <row r="173" customHeight="1" spans="1:26">
       <c r="A173" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
       <c r="D173" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E173" s="5"/>
       <c r="F173" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G173" s="4"/>
       <c r="H173" s="4"/>
@@ -22683,16 +22691,16 @@
     </row>
     <row r="174" customHeight="1" spans="1:26">
       <c r="A174" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
       <c r="D174" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E174" s="5"/>
       <c r="F174" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G174" s="4"/>
       <c r="H174" s="4"/>
@@ -22717,16 +22725,16 @@
     </row>
     <row r="175" customHeight="1" spans="1:26">
       <c r="A175" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
       <c r="D175" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E175" s="5"/>
       <c r="F175" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G175" s="4"/>
       <c r="H175" s="4"/>
@@ -22751,16 +22759,16 @@
     </row>
     <row r="176" customHeight="1" spans="1:26">
       <c r="A176" s="6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
       <c r="D176" s="6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E176" s="6"/>
       <c r="F176" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G176" s="4"/>
       <c r="H176" s="4"/>
@@ -22785,16 +22793,16 @@
     </row>
     <row r="177" customHeight="1" spans="1:26">
       <c r="A177" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G177" s="4"/>
       <c r="H177" s="4"/>
@@ -22819,16 +22827,16 @@
     </row>
     <row r="178" customHeight="1" spans="1:26">
       <c r="A178" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
       <c r="D178" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E178" s="5"/>
       <c r="F178" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G178" s="4"/>
       <c r="H178" s="4"/>
@@ -22853,16 +22861,16 @@
     </row>
     <row r="179" customHeight="1" spans="1:26">
       <c r="A179" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
       <c r="D179" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E179" s="5"/>
       <c r="F179" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G179" s="4"/>
       <c r="H179" s="4"/>
@@ -22887,16 +22895,16 @@
     </row>
     <row r="180" customHeight="1" spans="1:26">
       <c r="A180" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
       <c r="D180" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E180" s="5"/>
       <c r="F180" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G180" s="4"/>
       <c r="H180" s="4"/>
@@ -22921,16 +22929,16 @@
     </row>
     <row r="181" customHeight="1" spans="1:26">
       <c r="A181" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
       <c r="D181" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E181" s="6"/>
       <c r="F181" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G181" s="4"/>
       <c r="H181" s="4"/>
@@ -22955,16 +22963,16 @@
     </row>
     <row r="182" customHeight="1" spans="1:26">
       <c r="A182" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G182" s="4"/>
       <c r="H182" s="4"/>
@@ -22989,16 +22997,16 @@
     </row>
     <row r="183" customHeight="1" spans="1:26">
       <c r="A183" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
       <c r="D183" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E183" s="5"/>
       <c r="F183" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G183" s="4"/>
       <c r="H183" s="4"/>
@@ -23023,16 +23031,16 @@
     </row>
     <row r="184" customHeight="1" spans="1:26">
       <c r="A184" s="5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
       <c r="D184" s="5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E184" s="5"/>
       <c r="F184" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G184" s="4"/>
       <c r="H184" s="4"/>
@@ -23057,16 +23065,16 @@
     </row>
     <row r="185" customHeight="1" spans="1:26">
       <c r="A185" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
       <c r="D185" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E185" s="5"/>
       <c r="F185" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G185" s="4"/>
       <c r="H185" s="4"/>
@@ -23091,16 +23099,16 @@
     </row>
     <row r="186" customHeight="1" spans="1:26">
       <c r="A186" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
       <c r="D186" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E186" s="6"/>
       <c r="F186" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G186" s="4"/>
       <c r="H186" s="4"/>
@@ -23125,16 +23133,16 @@
     </row>
     <row r="187" customHeight="1" spans="1:26">
       <c r="A187" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G187" s="4"/>
       <c r="H187" s="4"/>
@@ -23159,16 +23167,16 @@
     </row>
     <row r="188" customHeight="1" spans="1:26">
       <c r="A188" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
       <c r="D188" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E188" s="5"/>
       <c r="F188" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G188" s="4"/>
       <c r="H188" s="4"/>
@@ -23193,16 +23201,16 @@
     </row>
     <row r="189" customHeight="1" spans="1:26">
       <c r="A189" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
       <c r="D189" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E189" s="5"/>
       <c r="F189" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G189" s="4"/>
       <c r="H189" s="4"/>
@@ -23227,16 +23235,16 @@
     </row>
     <row r="190" customHeight="1" spans="1:26">
       <c r="A190" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
       <c r="D190" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E190" s="5"/>
       <c r="F190" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G190" s="4"/>
       <c r="H190" s="4"/>
@@ -23261,16 +23269,16 @@
     </row>
     <row r="191" customHeight="1" spans="1:26">
       <c r="A191" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
       <c r="D191" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E191" s="6"/>
       <c r="F191" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G191" s="4"/>
       <c r="H191" s="4"/>
@@ -23295,16 +23303,16 @@
     </row>
     <row r="192" customHeight="1" spans="1:26">
       <c r="A192" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G192" s="4"/>
       <c r="H192" s="4"/>
@@ -23329,16 +23337,16 @@
     </row>
     <row r="193" customHeight="1" spans="1:26">
       <c r="A193" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
       <c r="D193" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E193" s="5"/>
       <c r="F193" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G193" s="4"/>
       <c r="H193" s="4"/>
@@ -23363,16 +23371,16 @@
     </row>
     <row r="194" customHeight="1" spans="1:26">
       <c r="A194" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
       <c r="D194" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E194" s="5"/>
       <c r="F194" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G194" s="4"/>
       <c r="H194" s="4"/>
@@ -23397,16 +23405,16 @@
     </row>
     <row r="195" customHeight="1" spans="1:26">
       <c r="A195" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
       <c r="D195" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E195" s="5"/>
       <c r="F195" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G195" s="4"/>
       <c r="H195" s="4"/>
@@ -23431,16 +23439,16 @@
     </row>
     <row r="196" customHeight="1" spans="1:26">
       <c r="A196" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
       <c r="D196" s="6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E196" s="6"/>
       <c r="F196" s="6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G196" s="4"/>
       <c r="H196" s="4"/>
@@ -23465,16 +23473,16 @@
     </row>
     <row r="197" customHeight="1" spans="1:26">
       <c r="A197" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G197" s="4"/>
       <c r="H197" s="4"/>
@@ -23499,16 +23507,16 @@
     </row>
     <row r="198" customHeight="1" spans="1:26">
       <c r="A198" s="5" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
       <c r="D198" s="5" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E198" s="5"/>
       <c r="F198" s="5" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G198" s="4"/>
       <c r="H198" s="4"/>
@@ -23533,16 +23541,16 @@
     </row>
     <row r="199" customHeight="1" spans="1:26">
       <c r="A199" s="5" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
       <c r="D199" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E199" s="5"/>
       <c r="F199" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
@@ -23567,16 +23575,16 @@
     </row>
     <row r="200" customHeight="1" spans="1:26">
       <c r="A200" s="5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
       <c r="D200" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E200" s="5"/>
       <c r="F200" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
@@ -23601,16 +23609,16 @@
     </row>
     <row r="201" customHeight="1" spans="1:26">
       <c r="A201" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B201" s="6"/>
       <c r="C201" s="6"/>
       <c r="D201" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E201" s="6"/>
       <c r="F201" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>

--- a/data/databook.xlsx
+++ b/data/databook.xlsx
@@ -233,7 +233,7 @@
     <t>caption</t>
   </si>
   <si>
-    <t>image</t>
+    <t>media</t>
   </si>
   <si>
     <t>comment</t>
@@ -310,22 +310,15 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\1.mp4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\1.mp4</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">FULL STORY IN HERE </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF800080"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
@@ -334,8 +327,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">👇👇:
@@ -345,8 +337,7 @@
       <rPr>
         <u/>
         <sz val="10"/>
-        <color rgb="FF800080"/>
-        <rFont val="宋体"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>https://story01.cotich.net/960687/</t>
@@ -393,11 +384,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\2.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\2.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/955865/</t>
+    </r>
   </si>
   <si>
     <t>POST_003</t>
@@ -441,11 +450,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\3.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\3.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/973291/</t>
+    </r>
   </si>
   <si>
     <t>POST_004</t>
@@ -524,11 +551,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\4.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\4.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/760390</t>
+    </r>
   </si>
   <si>
     <t>POST_005</t>
@@ -575,11 +620,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\5.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\5.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/589500</t>
+    </r>
   </si>
   <si>
     <t>POST_006</t>
@@ -754,11 +817,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\6.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\6.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/767626/</t>
+    </r>
   </si>
   <si>
     <t>POST_007</t>
@@ -802,11 +883,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\140.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\140.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/653532</t>
+    </r>
   </si>
   <si>
     <t>POST_008</t>
@@ -852,11 +951,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\8.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\8.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/553622/</t>
+    </r>
   </si>
   <si>
     <t>POST_009</t>
@@ -933,11 +1050,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\9.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\9.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/660134/</t>
+    </r>
   </si>
   <si>
     <t>POST_010</t>
@@ -982,11 +1117,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\10.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\10.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/421295</t>
+    </r>
   </si>
   <si>
     <t>POST_011</t>
@@ -1009,11 +1162,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\141.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\141.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/992662/</t>
+    </r>
   </si>
   <si>
     <t>POST_012</t>
@@ -1062,11 +1233,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\144.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\144.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/859295/</t>
+    </r>
   </si>
   <si>
     <t>POST_013</t>
@@ -1112,11 +1301,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\146.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\146.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/585874</t>
+    </r>
   </si>
   <si>
     <t>POST_014</t>
@@ -1148,11 +1355,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\147.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\147.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/477952</t>
+    </r>
   </si>
   <si>
     <t>POST_015</t>
@@ -1201,11 +1426,29 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>C:\Users\PC\Downloads\2051026\148.mp4</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <t>C:\Users\ADMIN\Downloads\Vid Dola\Vid cũ\20510\148.mp4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/895522/</t>
+    </r>
   </si>
   <si>
     <t>POST_016</t>
@@ -1336,8 +1579,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/789298</t>
+    </r>
   </si>
   <si>
     <t>POST_017</t>
@@ -1392,8 +1653,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/368452/</t>
+    </r>
   </si>
   <si>
     <t>POST_018</t>
@@ -1443,8 +1722,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/916777/</t>
+    </r>
   </si>
   <si>
     <t>POST_019</t>
@@ -1505,8 +1802,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/119617</t>
+    </r>
   </si>
   <si>
     <t>POST_020</t>
@@ -1557,8 +1872,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/395278/</t>
+    </r>
   </si>
   <si>
     <t>POST_021</t>
@@ -1641,8 +1974,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/400383</t>
+    </r>
   </si>
   <si>
     <t>POST_022</t>
@@ -1653,8 +2004,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/743691/</t>
+    </r>
   </si>
   <si>
     <t>POST_023</t>
@@ -1807,8 +2176,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/400658/</t>
+    </r>
   </si>
   <si>
     <t>POST_024</t>
@@ -1881,8 +2268,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/964346</t>
+    </r>
   </si>
   <si>
     <t>POST_025</t>
@@ -1970,8 +2375,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/799278/</t>
+    </r>
   </si>
   <si>
     <t>POST_026</t>
@@ -2025,8 +2448,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/161557/</t>
+    </r>
   </si>
   <si>
     <t>POST_027</t>
@@ -2067,8 +2508,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/145677</t>
+    </r>
   </si>
   <si>
     <t>POST_028</t>
@@ -2160,8 +2619,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/983385/</t>
+    </r>
   </si>
   <si>
     <t>POST_029</t>
@@ -2246,8 +2723,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/188843/</t>
+    </r>
   </si>
   <si>
     <t>POST_030</t>
@@ -2319,8 +2814,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/746098/</t>
+    </r>
   </si>
   <si>
     <t>POST_031</t>
@@ -2352,8 +2865,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/493384/</t>
+    </r>
   </si>
   <si>
     <t>POST_032</t>
@@ -2412,8 +2943,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/466308/</t>
+    </r>
   </si>
   <si>
     <t>POST_033</t>
@@ -2528,8 +3077,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/155548/</t>
+    </r>
   </si>
   <si>
     <t>POST_034</t>
@@ -2549,8 +3116,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/401194/</t>
+    </r>
   </si>
   <si>
     <t>POST_035</t>
@@ -2578,8 +3163,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/218909/</t>
+    </r>
   </si>
   <si>
     <t>POST_036</t>
@@ -2737,8 +3340,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/476252/</t>
+    </r>
   </si>
   <si>
     <t>POST_037</t>
@@ -2793,8 +3414,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/572000/</t>
+    </r>
   </si>
   <si>
     <t>POST_038</t>
@@ -2896,8 +3535,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/111350/</t>
+    </r>
   </si>
   <si>
     <t>POST_039</t>
@@ -2998,8 +3655,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/487744/</t>
+    </r>
   </si>
   <si>
     <t>POST_040</t>
@@ -3065,8 +3740,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/817546/</t>
+    </r>
   </si>
   <si>
     <t>POST_041</t>
@@ -3117,8 +3810,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/389155/</t>
+    </r>
   </si>
   <si>
     <t>POST_042</t>
@@ -3195,8 +3906,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/589681/</t>
+    </r>
   </si>
   <si>
     <t>POST_043</t>
@@ -3236,8 +3965,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/367882/</t>
+    </r>
   </si>
   <si>
     <t>POST_044</t>
@@ -3266,8 +4013,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/543573/</t>
+    </r>
   </si>
   <si>
     <t>POST_045</t>
@@ -3309,8 +4074,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/938730/</t>
+    </r>
   </si>
   <si>
     <t>POST_046</t>
@@ -3366,8 +4149,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/622018</t>
+    </r>
   </si>
   <si>
     <t>POST_047</t>
@@ -3418,8 +4219,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/311415/</t>
+    </r>
   </si>
   <si>
     <t>POST_048</t>
@@ -3448,8 +4267,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/773053/</t>
+    </r>
   </si>
   <si>
     <t>POST_049</t>
@@ -3495,8 +4332,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/718472/</t>
+    </r>
   </si>
   <si>
     <t>POST_050</t>
@@ -3512,8 +4367,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/131307/</t>
+    </r>
   </si>
   <si>
     <t>POST_051</t>
@@ -3536,8 +4409,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/286209/</t>
+    </r>
   </si>
   <si>
     <t>POST_052</t>
@@ -3578,8 +4469,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/607097/</t>
+    </r>
   </si>
   <si>
     <t>POST_053</t>
@@ -3598,8 +4507,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/677330/</t>
+    </r>
   </si>
   <si>
     <t>POST_054</t>
@@ -3690,8 +4617,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/812451/</t>
+    </r>
   </si>
   <si>
     <t>POST_055</t>
@@ -3786,8 +4731,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/211937/</t>
+    </r>
   </si>
   <si>
     <t>POST_056</t>
@@ -3808,8 +4771,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/102356/</t>
+    </r>
   </si>
   <si>
     <t>POST_057</t>
@@ -3867,8 +4848,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/721881/</t>
+    </r>
   </si>
   <si>
     <t>POST_058</t>
@@ -3886,8 +4885,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/457432/</t>
+    </r>
   </si>
   <si>
     <t>POST_059</t>
@@ -3921,8 +4938,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/543717/</t>
+    </r>
   </si>
   <si>
     <t>POST_060</t>
@@ -3971,8 +5006,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/897531/</t>
+    </r>
   </si>
   <si>
     <t>POST_061</t>
@@ -4025,8 +5078,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/514277/</t>
+    </r>
   </si>
   <si>
     <t>POST_062</t>
@@ -4092,8 +5163,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/446951/</t>
+    </r>
   </si>
   <si>
     <t>POST_063</t>
@@ -4176,8 +5265,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/540931/</t>
+    </r>
   </si>
   <si>
     <t>POST_064</t>
@@ -4218,8 +5325,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/446206/</t>
+    </r>
   </si>
   <si>
     <t>POST_065</t>
@@ -4245,8 +5370,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/261356/</t>
+    </r>
   </si>
   <si>
     <t>POST_066</t>
@@ -4326,8 +5469,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/886347/</t>
+    </r>
   </si>
   <si>
     <t>POST_067</t>
@@ -4391,8 +5552,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/746549/</t>
+    </r>
   </si>
   <si>
     <t>POST_068</t>
@@ -4549,8 +5728,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/370475/</t>
+    </r>
   </si>
   <si>
     <t>POST_069</t>
@@ -4651,8 +5848,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/595815/</t>
+    </r>
   </si>
   <si>
     <t>POST_070</t>
@@ -4738,8 +5953,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/331466/</t>
+    </r>
   </si>
   <si>
     <t>POST_071</t>
@@ -4776,8 +6009,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/138752/</t>
+    </r>
   </si>
   <si>
     <t>POST_072</t>
@@ -4852,8 +6103,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/263569/</t>
+    </r>
   </si>
   <si>
     <t>POST_073</t>
@@ -4878,8 +6147,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/411368/</t>
+    </r>
   </si>
   <si>
     <t>POST_074</t>
@@ -4931,8 +6218,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/984101/</t>
+    </r>
   </si>
   <si>
     <t>POST_075</t>
@@ -4986,8 +6291,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/660376/</t>
+    </r>
   </si>
   <si>
     <t>POST_076</t>
@@ -5083,8 +6406,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/979693/</t>
+    </r>
   </si>
   <si>
     <t>POST_077</t>
@@ -5159,8 +6500,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/206907</t>
+    </r>
   </si>
   <si>
     <t>POST_078</t>
@@ -5260,8 +6619,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/679773/</t>
+    </r>
   </si>
   <si>
     <t>POST_079</t>
@@ -5341,8 +6718,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/868457/</t>
+    </r>
   </si>
   <si>
     <t>POST_080</t>
@@ -5444,8 +6839,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/867153/</t>
+    </r>
   </si>
   <si>
     <t>POST_081</t>
@@ -5502,8 +6915,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/810504/</t>
+    </r>
   </si>
   <si>
     <t>POST_082</t>
@@ -5553,8 +6984,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/273987/</t>
+    </r>
   </si>
   <si>
     <t>POST_083</t>
@@ -5585,8 +7034,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/767805/</t>
+    </r>
   </si>
   <si>
     <t>POST_084</t>
@@ -5613,8 +7080,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/772348/</t>
+    </r>
   </si>
   <si>
     <t>POST_085</t>
@@ -5660,8 +7145,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/663622/</t>
+    </r>
   </si>
   <si>
     <t>POST_086</t>
@@ -5691,8 +7194,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/456790/</t>
+    </r>
   </si>
   <si>
     <t>POST_087</t>
@@ -5727,8 +7248,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/279183/</t>
+    </r>
   </si>
   <si>
     <t>POST_088</t>
@@ -5751,8 +7290,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/774680/</t>
+    </r>
   </si>
   <si>
     <t>POST_089</t>
@@ -5831,8 +7388,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/217905/</t>
+    </r>
   </si>
   <si>
     <t>POST_090</t>
@@ -5916,8 +7491,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/726391/</t>
+    </r>
   </si>
   <si>
     <t>POST_091</t>
@@ -5977,8 +7570,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/859342/</t>
+    </r>
   </si>
   <si>
     <t>POST_092</t>
@@ -6030,8 +7641,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/796638/</t>
+    </r>
   </si>
   <si>
     <t>POST_093</t>
@@ -6086,8 +7715,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/714208/</t>
+    </r>
   </si>
   <si>
     <t>POST_094</t>
@@ -6151,8 +7798,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/434830/</t>
+    </r>
   </si>
   <si>
     <t>POST_095</t>
@@ -6211,8 +7876,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/550014/</t>
+    </r>
   </si>
   <si>
     <t>POST_096</t>
@@ -6285,8 +7968,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/123753/</t>
+    </r>
   </si>
   <si>
     <t>POST_097</t>
@@ -6373,17 +8074,52 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/241930</t>
+    </r>
   </si>
   <si>
     <t>POST_098</t>
   </si>
   <si>
-    <t>My children brought me to the bank to prove I was too forgetful to handle my own money… but they forgot one thing: I had already seen the transaction they tried to hide. 🏦💵
+    <r>
+      <t xml:space="preserve">My children brought me to the bank to prove I was too forgetful to handle my own money… but they forgot one thing: I had already seen the transaction they tried to hide. 🏦💵
 They smiled at the manager, slid a power of attorney form across the desk, and spoke about me like I was not sitting right there.
 I signed nothing. I only asked for the restroom.
-Ten minutes later, I walked back in with the branch president beside me, my attorney on speakerphone, and one question that drained the color from all three of their faces. ⚖️
+Ten minutes later, I walked back in with the branch president beside me, my attorney on speakerphone, and one question that drained the color from all three of their faces. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>⚖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>️
 My name is Margaret Whitaker. I am seventy-four years old, a widow, and apparently just old enough for my children to mistake grief for weakness.
 After my husband Joseph died, they suddenly became very “helpful.”
 That was the word they used.
@@ -6440,10 +8176,29 @@
 And that was the moment I knew exactly how long they had been planning it.
 ————————————————————
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/691703/</t>
+    </r>
   </si>
   <si>
     <t>POST_099</t>
@@ -6514,8 +8269,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/330877/</t>
+    </r>
   </si>
   <si>
     <t>POST_100</t>
@@ -6578,18 +8351,69 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/262899/</t>
+    </r>
   </si>
   <si>
     <t>POST_101</t>
   </si>
   <si>
-    <t>My son called me and said, “Mom, we’ve moved to another state already—we forgot to tell you.” I was silent for five seconds. Then I replied, “Alright, son. Good luck.” I hung up, opened my laptop, and emailed my attorney before the coffee on my porch even went cold. ⚖️
+    <r>
+      <t xml:space="preserve">My son called me and said, “Mom, we’ve moved to another state already—we forgot to tell you.” I was silent for five seconds. Then I replied, “Alright, son. Good luck.” I hung up, opened my laptop, and emailed my attorney before the coffee on my porch even went cold. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>⚖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">️
 The call came on a gray Tuesday afternoon while I was sitting on my back porch with a mug of coffee warming between my hands. The whole neighborhood had that sleepy, ordinary sound to it — a lawn crew humming somewhere down the block, a delivery truck shifting gears at the corner, the loose edge of the porch screen tapping softly in the wind.
 When I saw my son’s name on my phone, I smiled before I could stop myself.
 That reflex never leaves a mother.
-No matter how old your child gets, some part of you still answers like he is ten years old and calling from the school office because he forgot his lunch. ☕
+No matter how old your child gets, some part of you still answers like he is ten years old and calling from the school office because he forgot his lunch. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>☕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 I expected something ordinary.
 Maybe he needed help with the kids this weekend. Maybe a school form. Maybe a bill that had landed at the wrong time. Maybe one of those “small emergencies” that always seemed to find my door before they found anyone else’s.
 I had a roast thawing in the fridge. A grocery list on the counter. Sunday dinner still written on my calendar like it meant something.
@@ -6638,7 +8462,23 @@
 Just names.
 Dates.
 Account details.
-And one attachment I had kept for years, hoping I would never have to use it. ⚖️
+And one attachment I had kept for years, hoping I would never have to use it. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>⚖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>️
 When I hit send, I did not feel cruel.
 I felt awake.
 By the time the coffee on the porch had gone cold, my attorney had replied with only six words:
@@ -6647,10 +8487,29 @@
 He had forgotten what I still controlled.
 ————————————————————
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/794710/</t>
+    </r>
   </si>
   <si>
     <t>POST_102</t>
@@ -6758,8 +8617,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/397393/</t>
+    </r>
   </si>
   <si>
     <t>POST_103</t>
@@ -6869,8 +8746,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/871888/</t>
+    </r>
   </si>
   <si>
     <t>POST_104</t>
@@ -6905,8 +8800,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/802976/</t>
+    </r>
   </si>
   <si>
     <t>POST_105</t>
@@ -6918,8 +8831,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/959970/</t>
+    </r>
   </si>
   <si>
     <t>POST_106</t>
@@ -7019,8 +8950,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/760716/</t>
+    </r>
   </si>
   <si>
     <t>POST_107</t>
@@ -7050,25 +8999,92 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/237139/</t>
+    </r>
   </si>
   <si>
     <t>POST_108</t>
   </si>
   <si>
-    <t>“Maybe you should eat upstairs,” my daughter-in-law said calmly as I was just about to sit down at the Christmas table I had been up since 4:30 a.m. preparing and cooking for. 🎄🍽️ But this was my house. So I took off my apron, walked to the head of the table, and did something that made all of her guests fall silent. 😶
+    <r>
+      <t xml:space="preserve">“Maybe you should eat upstairs,” my daughter-in-law said calmly as I was just about to sit down at the Christmas table I had been up since 4:30 a.m. preparing and cooking for. 🎄🍽️ But this was my house. So I took off my apron, walked to the head of the table, and did something that made all of her guests fall silent. 😶
 The cranberry sauce was still cooling beside the stove, and the turkey had that deep, buttery smell that settles into the walls when a house has been keeping Christmas the same way for a long time. 🦃🥣
-Outside, the streetlights on our block outside Columbus, Ohio, were reflecting off a thin layer of December ice. ❄️ Inside, my kitchen looked the way it always had on Christmas Eve. Good glasses polished. Walnut-handled cutlery laid out. The placemats I embroidered years ago pressed flat at every setting. I had been on my feet since 4:30 that morning, doing what I had done for decades without anyone needing to ask. 🕯️
+Outside, the streetlights on our block outside Columbus, Ohio, were reflecting off a thin layer of December ice. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">️ Inside, my kitchen looked the way it always had on Christmas Eve. Good glasses polished. Walnut-handled cutlery laid out. The placemats I embroidered years ago pressed flat at every setting. I had been on my feet since 4:30 that morning, doing what I had done for decades without anyone needing to ask. 🕯️
 That was part of why her voice hit me the way it did.
 Not loud. Not rude in the obvious way. Calm. Organized. Almost helpful.
-Like she was adjusting seating at a restaurant instead of informing me that I was somehow in the way at my own table. ⚠️
+Like she was adjusting seating at a restaurant instead of informing me that I was somehow in the way at my own table. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>⚠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">️
 I was still wearing my apron when she said it. My reading glasses were pushed up in my hair. My hands smelled faintly like rosemary and dish soap. 🌿🧼 And for one long second, I just stood there with a towel in my hand, looking at the woman who had been living in my house long enough to start speaking as if comfort belonged to her more than memory belonged to me.
 The hard part is this did not begin on Christmas.
 It began the way these things usually begin in families that are trying too hard to stay polite.
 A small favor. A temporary arrangement. A son calling to say things had gotten tight. A daughter-in-law between jobs and trying to get something of her own off the ground. A promise that it would only be for a few months while they got back on their feet. 🏠
 And because I was a mother before I was anything else, I said yes too fast.
-At first it was easy to excuse the little things. A pillow moved. A framed piece taken down and replaced with something “cleaner.” Kitchen shelves reorganized for “function.” My favorite mug pushed behind a row of matching white ones because mine was “a little uneven.” ☕ Rooms I had used for years suddenly being discussed as if they were flexible space.
+At first it was easy to excuse the little things. A pillow moved. A framed piece taken down and replaced with something “cleaner.” Kitchen shelves reorganized for “function.” My favorite mug pushed behind a row of matching white ones because mine was “a little uneven.” </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>☕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Rooms I had used for years suddenly being discussed as if they were flexible space.
 My home slowly edited around me in tiny, tidy decisions no one felt large enough to fight about on their own.
 That is how you become a guest in your own life. 💔
 Not all at once.
@@ -7086,10 +9102,29 @@
 And I walked toward the head of the table. 🔥
 ————————————————————
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/732076/</t>
+    </r>
   </si>
   <si>
     <t>POST_109</t>
@@ -7173,14 +9208,33 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/901076/</t>
+    </r>
   </si>
   <si>
     <t>POST_110</t>
   </si>
   <si>
-    <t>Evelyn came to bless her daughter with the family pearls… but Grace blocked the bridal-room door and whispered, “Mom, I’m sorry. You can’t stay.” 😔💔 Behind her, the country-club ballroom glowed with flowers, candles, and music — all paid for by Evelyn — and the groom’s mother smiled, not knowing Evelyn’s name was still attached to the one thing keeping that perfect wedding alive.
+    <r>
+      <t xml:space="preserve">Evelyn came to bless her daughter with the family pearls… but Grace blocked the bridal-room door and whispered, “Mom, I’m sorry. You can’t stay.” 😔💔 Behind her, the country-club ballroom glowed with flowers, candles, and music — all paid for by Evelyn — and the groom’s mother smiled, not knowing Evelyn’s name was still attached to the one thing keeping that perfect wedding alive.
 For a moment, Evelyn thought she had misheard.
 She stood there in her soft blue dress, one hand wrapped around the little velvet box, staring at the daughter she had raised by herself since Grace was seven years old.
 This was supposed to be the quiet moment before the ceremony.
@@ -7230,7 +9284,23 @@
 The champagne flowed.
 And Evelyn finally understood the truth: they had not only taken her money.
 They had counted on her shame keeping her quiet.
-But shame has a strange way of dying when a woman has nothing left to protect except her dignity. ⚖️
+But shame has a strange way of dying when a woman has nothing left to protect except her dignity. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>⚖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>️
 Evelyn picked up her phone.
 Her hand was steady now.
 She scrolled past Grace’s name, past the family group chat, past every person who would have told her to calm down and “not ruin the day.”
@@ -7248,10 +9318,29 @@
 Twenty-three minutes later, the first light in the ballroom went dark… and Grace finally turned toward the door with fear on her face.
 ————————————————————
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/231602/</t>
+    </r>
   </si>
   <si>
     <t>POST_111</t>
@@ -7297,8 +9386,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/410726/</t>
+    </r>
   </si>
   <si>
     <t>POST_112</t>
@@ -7332,8 +9439,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/437398/</t>
+    </r>
   </si>
   <si>
     <t>POST_113</t>
@@ -7431,8 +9556,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/833876/</t>
+    </r>
   </si>
   <si>
     <t>POST_114</t>
@@ -7510,8 +9653,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/439802/</t>
+    </r>
   </si>
   <si>
     <t>POST_115</t>
@@ -7598,8 +9759,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/566870/</t>
+    </r>
   </si>
   <si>
     <t>POST_116</t>
@@ -7711,8 +9890,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/596390/</t>
+    </r>
   </si>
   <si>
     <t>POST_117</t>
@@ -7809,8 +10006,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/289848/</t>
+    </r>
   </si>
   <si>
     <t>POST_118</t>
@@ -7849,8 +10064,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/782144/</t>
+    </r>
   </si>
   <si>
     <t>POST_119</t>
@@ -7895,8 +10128,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/723119/</t>
+    </r>
   </si>
   <si>
     <t>POST_120</t>
@@ -8079,8 +10330,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/709275/</t>
+    </r>
   </si>
   <si>
     <t>POST_121</t>
@@ -8127,8 +10396,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/418991/</t>
+    </r>
   </si>
   <si>
     <t>POST_122</t>
@@ -8153,8 +10440,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/208650/</t>
+    </r>
   </si>
   <si>
     <t>POST_123</t>
@@ -8205,8 +10510,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/910008/</t>
+    </r>
   </si>
   <si>
     <t>POST_124</t>
@@ -8303,8 +10626,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/135366/</t>
+    </r>
   </si>
   <si>
     <t>POST_125</t>
@@ -8361,8 +10702,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/875623/</t>
+    </r>
   </si>
   <si>
     <t>POST_126</t>
@@ -8467,8 +10826,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/172488/</t>
+    </r>
   </si>
   <si>
     <t>POST_127</t>
@@ -8576,8 +10953,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/796857/</t>
+    </r>
   </si>
   <si>
     <t>POST_128</t>
@@ -8724,8 +11119,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/146958/</t>
+    </r>
   </si>
   <si>
     <t>POST_129</t>
@@ -8868,8 +11281,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/679714/</t>
+    </r>
   </si>
   <si>
     <t>POST_130</t>
@@ -8977,8 +11408,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/826080/</t>
+    </r>
   </si>
   <si>
     <t>POST_131</t>
@@ -9109,8 +11558,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/816093/</t>
+    </r>
   </si>
   <si>
     <t>POST_132</t>
@@ -9191,8 +11658,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/768511/</t>
+    </r>
   </si>
   <si>
     <t>POST_133</t>
@@ -9271,8 +11756,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/723717/</t>
+    </r>
   </si>
   <si>
     <t>POST_134</t>
@@ -9304,8 +11807,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/337368/</t>
+    </r>
   </si>
   <si>
     <t>POST_135</t>
@@ -9451,8 +11972,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/729687/</t>
+    </r>
   </si>
   <si>
     <t>POST_136</t>
@@ -9474,8 +12013,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/656845/</t>
+    </r>
   </si>
   <si>
     <t>POST_137</t>
@@ -9578,8 +12135,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/935651/</t>
+    </r>
   </si>
   <si>
     <t>POST_138</t>
@@ -9655,8 +12230,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/106452/</t>
+    </r>
   </si>
   <si>
     <t>POST_139</t>
@@ -9712,8 +12305,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/613213/</t>
+    </r>
   </si>
   <si>
     <t>POST_140</t>
@@ -9845,8 +12456,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/596052/</t>
+    </r>
   </si>
   <si>
     <t>POST_141</t>
@@ -9963,8 +12592,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/242815/</t>
+    </r>
   </si>
   <si>
     <t>POST_142</t>
@@ -10014,8 +12661,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/205796/</t>
+    </r>
   </si>
   <si>
     <t>POST_143</t>
@@ -10152,8 +12817,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/631433/</t>
+    </r>
   </si>
   <si>
     <t>POST_144</t>
@@ -10237,8 +12920,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/999718/</t>
+    </r>
   </si>
   <si>
     <t>POST_145</t>
@@ -10361,8 +13062,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/100063/</t>
+    </r>
   </si>
   <si>
     <t>POST_146</t>
@@ -10489,8 +13208,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/417223/</t>
+    </r>
   </si>
   <si>
     <t>POST_147</t>
@@ -10563,8 +13300,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/786887/</t>
+    </r>
   </si>
   <si>
     <t>POST_148</t>
@@ -10696,8 +13451,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/909424/</t>
+    </r>
   </si>
   <si>
     <t>POST_149</t>
@@ -10740,8 +13513,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/612182/</t>
+    </r>
   </si>
   <si>
     <t>POST_150</t>
@@ -10842,8 +13633,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/536275/</t>
+    </r>
   </si>
   <si>
     <t>POST_151</t>
@@ -10918,8 +13727,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/718852/</t>
+    </r>
   </si>
   <si>
     <t>POST_152</t>
@@ -11063,8 +13890,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/516461/</t>
+    </r>
   </si>
   <si>
     <t>POST_153</t>
@@ -11118,8 +13963,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/561933/</t>
+    </r>
   </si>
   <si>
     <t>POST_154</t>
@@ -11426,8 +14289,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/107408/</t>
+    </r>
   </si>
   <si>
     <t>POST_155</t>
@@ -11528,8 +14409,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/845957/</t>
+    </r>
   </si>
   <si>
     <t>POST_156</t>
@@ -11573,8 +14472,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/591327/</t>
+    </r>
   </si>
   <si>
     <t>POST_157</t>
@@ -11650,8 +14567,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/181407/</t>
+    </r>
   </si>
   <si>
     <t>POST_158</t>
@@ -11692,8 +14627,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/821375/</t>
+    </r>
   </si>
   <si>
     <t>POST_159</t>
@@ -11714,8 +14667,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/873237/</t>
+    </r>
   </si>
   <si>
     <t>POST_160</t>
@@ -11763,8 +14734,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/663284/</t>
+    </r>
   </si>
   <si>
     <t>POST_161</t>
@@ -11841,8 +14830,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/593522/</t>
+    </r>
   </si>
   <si>
     <t>POST_162</t>
@@ -11913,8 +14920,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/429063/</t>
+    </r>
   </si>
   <si>
     <t>POST_163</t>
@@ -11943,8 +14968,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/835521/</t>
+    </r>
   </si>
   <si>
     <t>POST_164</t>
@@ -12064,8 +15107,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/952005/</t>
+    </r>
   </si>
   <si>
     <t>POST_165</t>
@@ -12196,8 +15257,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/937380/</t>
+    </r>
   </si>
   <si>
     <t>POST_166</t>
@@ -12270,8 +15349,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/872572/</t>
+    </r>
   </si>
   <si>
     <t>POST_167</t>
@@ -12455,8 +15552,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/863839/</t>
+    </r>
   </si>
   <si>
     <t>POST_168</t>
@@ -12638,8 +15753,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/553742/</t>
+    </r>
   </si>
   <si>
     <t>POST_169</t>
@@ -12795,8 +15928,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/215443/</t>
+    </r>
   </si>
   <si>
     <t>POST_170</t>
@@ -12999,8 +16150,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/620738/</t>
+    </r>
   </si>
   <si>
     <t>POST_171</t>
@@ -13146,8 +16315,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/397858/</t>
+    </r>
   </si>
   <si>
     <t>POST_172</t>
@@ -13175,8 +16362,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/480372/</t>
+    </r>
   </si>
   <si>
     <t>POST_173</t>
@@ -13257,8 +16462,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/843120/</t>
+    </r>
   </si>
   <si>
     <t>POST_174</t>
@@ -13412,8 +16635,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/250050/</t>
+    </r>
   </si>
   <si>
     <t>POST_175</t>
@@ -13487,8 +16728,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/803601/</t>
+    </r>
   </si>
   <si>
     <t>POST_176</t>
@@ -13559,8 +16818,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/594902/</t>
+    </r>
   </si>
   <si>
     <t>POST_177</t>
@@ -13624,14 +16901,33 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/561340/</t>
+    </r>
   </si>
   <si>
     <t>POST_178</t>
   </si>
   <si>
-    <t>My daughter-in-law said bluntly, ""My whole family is having Christmas at your house-it's only 25 people."" I smiled and said, ""Perfect. I'll be traveling for a few days. If you're the one inviting guests, then you can handle the cooking and the cleanup -I'm not here to play housekeeper in my own home."" She froze like she couldn't believe I'd actually say that... and right then, she realized the real ""gift"" of this holiday season had only just begun. 🎁
+    <r>
+      <t xml:space="preserve">My daughter-in-law said bluntly, ""My whole family is having Christmas at your house-it's only 25 people."" I smiled and said, ""Perfect. I'll be traveling for a few days. If you're the one inviting guests, then you can handle the cooking and the cleanup -I'm not here to play housekeeper in my own home."" She froze like she couldn't believe I'd actually say that... and right then, she realized the real ""gift"" of this holiday season had only just begun. 🎁
 It was a Tuesday in December, the kind of cold evening where the cul-de-sac looks postcard-pretty: porch lights glowing, inflatable Santas leaning slightly in the wind, and the HOA mailboxes lined up like little soldiers. I’d just slid a Costco tray into the fridge, paper plates tucked under the counter for the grandkids, when Tiffany swept into my kitchen like it was her staging area—heels clicking, lipstick perfect, smile already switched on. 🏡
 She sat down without waiting to be invited and started listing names like a guest manifest.
 “My sister Valyria and her kids. Uncle Alejandro. Cousins, nieces… a few friends.”
@@ -13655,7 +16951,23 @@
 Work shoes by the entryway.
 He walked in with his lobby badge still on, like he hadn’t even had time to breathe, and Tiffany rushed him immediately. 🚪
 “Mom,” Kevin started, rubbing his forehead, “Tiffany says you’re refusing to help. It’s the holidays.”
-“I’m not refusing Christmas,” I said. “I’m refusing to be volunteered.” ⚠️
+“I’m not refusing Christmas,” I said. “I’m refusing to be volunteered.” </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>⚠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>️
 Tiffany jumped in.
 “We can’t afford catering. Everything’s booked.”
 Kevin looked away and muttered, almost under his breath, “The apartment deposit wiped out our savings…”
@@ -13675,10 +16987,29 @@
 She had no idea what I was about to send. 📩
 ————————————————————
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
-  </si>
-  <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/387944/</t>
+    </r>
   </si>
   <si>
     <t>POST_179</t>
@@ -13790,8 +17121,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/937182/</t>
+    </r>
   </si>
   <si>
     <t>POST_180</t>
@@ -13833,8 +17182,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/911304/</t>
+    </r>
   </si>
   <si>
     <t>POST_181</t>
@@ -13875,8 +17242,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/999502/</t>
+    </r>
   </si>
   <si>
     <t>POST_182</t>
@@ -13929,8 +17314,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/820054/</t>
+    </r>
   </si>
   <si>
     <t>POST_183</t>
@@ -13949,8 +17352,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/519078/</t>
+    </r>
   </si>
   <si>
     <t>POST_184</t>
@@ -13979,8 +17400,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/844927/</t>
+    </r>
   </si>
   <si>
     <t>POST_185</t>
@@ -14051,8 +17490,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/787018/</t>
+    </r>
   </si>
   <si>
     <t>POST_186</t>
@@ -14114,8 +17571,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/903941/</t>
+    </r>
   </si>
   <si>
     <t>POST_187</t>
@@ -14160,8 +17635,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/670057/</t>
+    </r>
   </si>
   <si>
     <t>POST_188</t>
@@ -14186,8 +17679,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/853260/</t>
+    </r>
   </si>
   <si>
     <t>POST_189</t>
@@ -14198,8 +17709,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/460431</t>
+    </r>
   </si>
   <si>
     <t>POST_190</t>
@@ -14233,8 +17762,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/664104</t>
+    </r>
   </si>
   <si>
     <t>POST_191</t>
@@ -14245,8 +17792,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/596493</t>
+    </r>
   </si>
   <si>
     <t>POST_192</t>
@@ -14280,8 +17845,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/831458</t>
+    </r>
   </si>
   <si>
     <t>POST_193</t>
@@ -14435,8 +18018,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/183052/</t>
+    </r>
   </si>
   <si>
     <t>POST_194</t>
@@ -14482,8 +18083,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/611665</t>
+    </r>
   </si>
   <si>
     <t>POST_195</t>
@@ -14528,8 +18147,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/457870/</t>
+    </r>
   </si>
   <si>
     <t>POST_196</t>
@@ -14611,8 +18248,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/848619/</t>
+    </r>
   </si>
   <si>
     <t>POST_197</t>
@@ -14655,8 +18310,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/566195</t>
+    </r>
   </si>
   <si>
     <t>POST_198</t>
@@ -14729,8 +18402,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/773227/</t>
+    </r>
   </si>
   <si>
     <t>POST_199</t>
@@ -14923,8 +18614,26 @@
 As Facebook doesn't allow us to write more, you can read more under the comment section. If you don't see the link, you can adjust the Most Relevant Comments Option to All Comments 👇👇👇</t>
   </si>
   <si>
-    <t>FULL STORY IN HERE ❤👇👇:
+    <r>
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>👇👇:
 https://story01.cotich.net/480846/</t>
+    </r>
   </si>
   <si>
     <t>POST_200</t>
@@ -14957,20 +18666,30 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">FULL STORY IN HERE ❤👇👇:
+      <t xml:space="preserve">FULL STORY IN HERE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>❤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">👇👇:
 </t>
     </r>
     <r>
       <rPr>
         <u/>
         <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="宋体"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>https://story01.cotich.net/535863/</t>
@@ -14987,13 +18706,24 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -15006,20 +18736,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -15046,6 +18762,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -15192,27 +18916,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF800080"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF1155CC"/>
-      <name val="宋体"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -15577,31 +19287,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -15610,152 +19317,153 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="6" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16538,19 +20246,19 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
@@ -16766,41 +20474,43 @@
   <dimension ref="A1:Z201"/>
   <sheetFormatPr defaultColWidth="12.6285714285714" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="4" max="4" width="61.5047619047619" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="38.247619047619" customWidth="1"/>
+    <col min="1" max="3" width="12.6285714285714" style="1"/>
+    <col min="4" max="4" width="61.5047619047619" style="1" customWidth="1"/>
+    <col min="5" max="5" width="52" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.247619047619" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="12.6285714285714" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:26">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -16835,7 +20545,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>74</v>
@@ -16911,7 +20621,7 @@
         <v>43</v>
       </c>
       <c r="C5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>82</v>
@@ -16980,22 +20690,22 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" customHeight="1" spans="1:26">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>3</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G7" s="4"/>
@@ -17172,18 +20882,18 @@
       <c r="Z11" s="4"/>
     </row>
     <row r="12" customHeight="1" spans="1:26">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G12" s="4"/>
@@ -17352,16 +21062,16 @@
       <c r="Z16" s="4"/>
     </row>
     <row r="17" customHeight="1" spans="1:26">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
         <v>131</v>
       </c>
       <c r="G17" s="4"/>
@@ -17522,16 +21232,16 @@
       <c r="Z21" s="4"/>
     </row>
     <row r="22" customHeight="1" spans="1:26">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2" t="s">
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G22" s="4"/>
@@ -17692,16 +21402,16 @@
       <c r="Z26" s="4"/>
     </row>
     <row r="27" customHeight="1" spans="1:26">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2" t="s">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2" t="s">
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="s">
         <v>161</v>
       </c>
       <c r="G27" s="4"/>
@@ -17862,16 +21572,16 @@
       <c r="Z31" s="4"/>
     </row>
     <row r="32" customHeight="1" spans="1:26">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2" t="s">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2" t="s">
+      <c r="E32" s="3"/>
+      <c r="F32" s="3" t="s">
         <v>176</v>
       </c>
       <c r="G32" s="4"/>
@@ -18032,16 +21742,16 @@
       <c r="Z36" s="4"/>
     </row>
     <row r="37" customHeight="1" spans="1:26">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2" t="s">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2" t="s">
+      <c r="E37" s="3"/>
+      <c r="F37" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G37" s="4"/>
@@ -18202,16 +21912,16 @@
       <c r="Z41" s="4"/>
     </row>
     <row r="42" customHeight="1" spans="1:26">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2" t="s">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2" t="s">
+      <c r="E42" s="3"/>
+      <c r="F42" s="3" t="s">
         <v>206</v>
       </c>
       <c r="G42" s="4"/>
@@ -18372,16 +22082,16 @@
       <c r="Z46" s="4"/>
     </row>
     <row r="47" customHeight="1" spans="1:26">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2" t="s">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2" t="s">
+      <c r="E47" s="3"/>
+      <c r="F47" s="3" t="s">
         <v>221</v>
       </c>
       <c r="G47" s="4"/>
@@ -18542,16 +22252,16 @@
       <c r="Z51" s="4"/>
     </row>
     <row r="52" customHeight="1" spans="1:26">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2" t="s">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2" t="s">
+      <c r="E52" s="3"/>
+      <c r="F52" s="3" t="s">
         <v>236</v>
       </c>
       <c r="G52" s="4"/>
@@ -18712,16 +22422,16 @@
       <c r="Z56" s="4"/>
     </row>
     <row r="57" customHeight="1" spans="1:26">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2" t="s">
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2" t="s">
+      <c r="E57" s="3"/>
+      <c r="F57" s="3" t="s">
         <v>251</v>
       </c>
       <c r="G57" s="4"/>
@@ -18882,16 +22592,16 @@
       <c r="Z61" s="4"/>
     </row>
     <row r="62" customHeight="1" spans="1:26">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2" t="s">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2" t="s">
+      <c r="E62" s="3"/>
+      <c r="F62" s="3" t="s">
         <v>266</v>
       </c>
       <c r="G62" s="4"/>
@@ -19052,16 +22762,16 @@
       <c r="Z66" s="4"/>
     </row>
     <row r="67" customHeight="1" spans="1:26">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2" t="s">
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2" t="s">
+      <c r="E67" s="3"/>
+      <c r="F67" s="3" t="s">
         <v>281</v>
       </c>
       <c r="G67" s="4"/>
@@ -19222,16 +22932,16 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" customHeight="1" spans="1:26">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2" t="s">
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2" t="s">
+      <c r="E72" s="3"/>
+      <c r="F72" s="3" t="s">
         <v>296</v>
       </c>
       <c r="G72" s="4"/>
@@ -19392,16 +23102,16 @@
       <c r="Z76" s="4"/>
     </row>
     <row r="77" customHeight="1" spans="1:26">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2" t="s">
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2" t="s">
+      <c r="E77" s="3"/>
+      <c r="F77" s="3" t="s">
         <v>311</v>
       </c>
       <c r="G77" s="4"/>
@@ -19562,16 +23272,16 @@
       <c r="Z81" s="4"/>
     </row>
     <row r="82" customHeight="1" spans="1:26">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2" t="s">
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2" t="s">
+      <c r="E82" s="3"/>
+      <c r="F82" s="3" t="s">
         <v>326</v>
       </c>
       <c r="G82" s="4"/>
@@ -19732,16 +23442,16 @@
       <c r="Z86" s="4"/>
     </row>
     <row r="87" customHeight="1" spans="1:26">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2" t="s">
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2" t="s">
+      <c r="E87" s="3"/>
+      <c r="F87" s="3" t="s">
         <v>341</v>
       </c>
       <c r="G87" s="4"/>
@@ -19902,16 +23612,16 @@
       <c r="Z91" s="4"/>
     </row>
     <row r="92" customHeight="1" spans="1:26">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2" t="s">
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2" t="s">
+      <c r="E92" s="3"/>
+      <c r="F92" s="3" t="s">
         <v>356</v>
       </c>
       <c r="G92" s="4"/>
@@ -20072,16 +23782,16 @@
       <c r="Z96" s="4"/>
     </row>
     <row r="97" customHeight="1" spans="1:26">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2" t="s">
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2" t="s">
+      <c r="E97" s="3"/>
+      <c r="F97" s="3" t="s">
         <v>371</v>
       </c>
       <c r="G97" s="4"/>
@@ -20242,16 +23952,16 @@
       <c r="Z101" s="4"/>
     </row>
     <row r="102" customHeight="1" spans="1:26">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2" t="s">
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2" t="s">
+      <c r="E102" s="3"/>
+      <c r="F102" s="3" t="s">
         <v>386</v>
       </c>
       <c r="G102" s="4"/>
@@ -20412,16 +24122,16 @@
       <c r="Z106" s="4"/>
     </row>
     <row r="107" customHeight="1" spans="1:26">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2" t="s">
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2" t="s">
+      <c r="E107" s="3"/>
+      <c r="F107" s="3" t="s">
         <v>401</v>
       </c>
       <c r="G107" s="4"/>
@@ -20582,16 +24292,16 @@
       <c r="Z111" s="4"/>
     </row>
     <row r="112" customHeight="1" spans="1:26">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2" t="s">
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2" t="s">
+      <c r="E112" s="3"/>
+      <c r="F112" s="3" t="s">
         <v>416</v>
       </c>
       <c r="G112" s="4"/>
@@ -20752,16 +24462,16 @@
       <c r="Z116" s="4"/>
     </row>
     <row r="117" customHeight="1" spans="1:26">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2" t="s">
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2" t="s">
+      <c r="E117" s="3"/>
+      <c r="F117" s="3" t="s">
         <v>431</v>
       </c>
       <c r="G117" s="4"/>
@@ -20922,16 +24632,16 @@
       <c r="Z121" s="4"/>
     </row>
     <row r="122" customHeight="1" spans="1:26">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2" t="s">
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2" t="s">
+      <c r="E122" s="3"/>
+      <c r="F122" s="3" t="s">
         <v>446</v>
       </c>
       <c r="G122" s="4"/>
@@ -21092,16 +24802,16 @@
       <c r="Z126" s="4"/>
     </row>
     <row r="127" customHeight="1" spans="1:26">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2" t="s">
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="E127" s="2"/>
-      <c r="F127" s="2" t="s">
+      <c r="E127" s="3"/>
+      <c r="F127" s="3" t="s">
         <v>461</v>
       </c>
       <c r="G127" s="4"/>
@@ -21262,16 +24972,16 @@
       <c r="Z131" s="4"/>
     </row>
     <row r="132" customHeight="1" spans="1:26">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2" t="s">
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2" t="s">
+      <c r="E132" s="3"/>
+      <c r="F132" s="3" t="s">
         <v>476</v>
       </c>
       <c r="G132" s="4"/>
@@ -21432,16 +25142,16 @@
       <c r="Z136" s="4"/>
     </row>
     <row r="137" customHeight="1" spans="1:26">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2" t="s">
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="E137" s="2"/>
-      <c r="F137" s="2" t="s">
+      <c r="E137" s="3"/>
+      <c r="F137" s="3" t="s">
         <v>491</v>
       </c>
       <c r="G137" s="4"/>
@@ -21602,16 +25312,16 @@
       <c r="Z141" s="4"/>
     </row>
     <row r="142" customHeight="1" spans="1:26">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2" t="s">
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="E142" s="2"/>
-      <c r="F142" s="2" t="s">
+      <c r="E142" s="3"/>
+      <c r="F142" s="3" t="s">
         <v>506</v>
       </c>
       <c r="G142" s="4"/>
@@ -21772,16 +25482,16 @@
       <c r="Z146" s="4"/>
     </row>
     <row r="147" customHeight="1" spans="1:26">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2" t="s">
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="E147" s="2"/>
-      <c r="F147" s="2" t="s">
+      <c r="E147" s="3"/>
+      <c r="F147" s="3" t="s">
         <v>521</v>
       </c>
       <c r="G147" s="4"/>
@@ -21942,16 +25652,16 @@
       <c r="Z151" s="4"/>
     </row>
     <row r="152" customHeight="1" spans="1:26">
-      <c r="A152" s="2" t="s">
+      <c r="A152" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
-      <c r="D152" s="2" t="s">
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="E152" s="2"/>
-      <c r="F152" s="2" t="s">
+      <c r="E152" s="3"/>
+      <c r="F152" s="3" t="s">
         <v>536</v>
       </c>
       <c r="G152" s="4"/>
@@ -22112,16 +25822,16 @@
       <c r="Z156" s="4"/>
     </row>
     <row r="157" customHeight="1" spans="1:26">
-      <c r="A157" s="2" t="s">
+      <c r="A157" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2" t="s">
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="E157" s="2"/>
-      <c r="F157" s="2" t="s">
+      <c r="E157" s="3"/>
+      <c r="F157" s="3" t="s">
         <v>551</v>
       </c>
       <c r="G157" s="4"/>
@@ -22282,16 +25992,16 @@
       <c r="Z161" s="4"/>
     </row>
     <row r="162" customHeight="1" spans="1:26">
-      <c r="A162" s="2" t="s">
+      <c r="A162" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
-      <c r="D162" s="2" t="s">
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="E162" s="2"/>
-      <c r="F162" s="2" t="s">
+      <c r="E162" s="3"/>
+      <c r="F162" s="3" t="s">
         <v>566</v>
       </c>
       <c r="G162" s="4"/>
@@ -22452,16 +26162,16 @@
       <c r="Z166" s="4"/>
     </row>
     <row r="167" customHeight="1" spans="1:26">
-      <c r="A167" s="2" t="s">
+      <c r="A167" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B167" s="2"/>
-      <c r="C167" s="2"/>
-      <c r="D167" s="2" t="s">
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="E167" s="2"/>
-      <c r="F167" s="2" t="s">
+      <c r="E167" s="3"/>
+      <c r="F167" s="3" t="s">
         <v>581</v>
       </c>
       <c r="G167" s="4"/>
@@ -22622,16 +26332,16 @@
       <c r="Z171" s="4"/>
     </row>
     <row r="172" customHeight="1" spans="1:26">
-      <c r="A172" s="2" t="s">
+      <c r="A172" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2" t="s">
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2" t="s">
+      <c r="E172" s="3"/>
+      <c r="F172" s="3" t="s">
         <v>596</v>
       </c>
       <c r="G172" s="4"/>
@@ -22792,16 +26502,16 @@
       <c r="Z176" s="4"/>
     </row>
     <row r="177" customHeight="1" spans="1:26">
-      <c r="A177" s="2" t="s">
+      <c r="A177" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="B177" s="2"/>
-      <c r="C177" s="2"/>
-      <c r="D177" s="2" t="s">
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="E177" s="2"/>
-      <c r="F177" s="2" t="s">
+      <c r="E177" s="3"/>
+      <c r="F177" s="3" t="s">
         <v>611</v>
       </c>
       <c r="G177" s="4"/>
@@ -22962,16 +26672,16 @@
       <c r="Z181" s="4"/>
     </row>
     <row r="182" customHeight="1" spans="1:26">
-      <c r="A182" s="2" t="s">
+      <c r="A182" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="B182" s="2"/>
-      <c r="C182" s="2"/>
-      <c r="D182" s="2" t="s">
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="E182" s="2"/>
-      <c r="F182" s="2" t="s">
+      <c r="E182" s="3"/>
+      <c r="F182" s="3" t="s">
         <v>626</v>
       </c>
       <c r="G182" s="4"/>
@@ -23132,16 +26842,16 @@
       <c r="Z186" s="4"/>
     </row>
     <row r="187" customHeight="1" spans="1:26">
-      <c r="A187" s="2" t="s">
+      <c r="A187" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="B187" s="2"/>
-      <c r="C187" s="2"/>
-      <c r="D187" s="2" t="s">
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="E187" s="2"/>
-      <c r="F187" s="2" t="s">
+      <c r="E187" s="3"/>
+      <c r="F187" s="3" t="s">
         <v>641</v>
       </c>
       <c r="G187" s="4"/>
@@ -23302,16 +27012,16 @@
       <c r="Z191" s="4"/>
     </row>
     <row r="192" customHeight="1" spans="1:26">
-      <c r="A192" s="2" t="s">
+      <c r="A192" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B192" s="2"/>
-      <c r="C192" s="2"/>
-      <c r="D192" s="2" t="s">
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="E192" s="2"/>
-      <c r="F192" s="2" t="s">
+      <c r="E192" s="3"/>
+      <c r="F192" s="3" t="s">
         <v>656</v>
       </c>
       <c r="G192" s="4"/>
@@ -23472,16 +27182,16 @@
       <c r="Z196" s="4"/>
     </row>
     <row r="197" customHeight="1" spans="1:26">
-      <c r="A197" s="2" t="s">
+      <c r="A197" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="B197" s="2"/>
-      <c r="C197" s="2"/>
-      <c r="D197" s="2" t="s">
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="E197" s="2"/>
-      <c r="F197" s="2" t="s">
+      <c r="E197" s="3"/>
+      <c r="F197" s="3" t="s">
         <v>671</v>
       </c>
       <c r="G197" s="4"/>
@@ -23617,7 +27327,7 @@
         <v>682</v>
       </c>
       <c r="E201" s="6"/>
-      <c r="F201" s="7" t="s">
+      <c r="F201" s="6" t="s">
         <v>683</v>
       </c>
       <c r="G201" s="4"/>
